--- a/knowledge/Datos_plano.xlsx
+++ b/knowledge/Datos_plano.xlsx
@@ -1,33 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marii\OneDrive\Documents\Formatos\Generador PDF\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2881CC-82DC-4E5A-BDDD-EF8F82243461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -36,111 +20,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>Atributo</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Nombre - representante legal:</t>
-  </si>
-  <si>
-    <t>Daniel Andrés Villa Llano</t>
-  </si>
-  <si>
-    <t>Cédula - representante legal:</t>
-  </si>
-  <si>
-    <t>Celular - representante legal:</t>
-  </si>
-  <si>
-    <t>Matrícula profesional - representante legal:</t>
-  </si>
-  <si>
-    <t>011037-0508328 ANT</t>
-  </si>
-  <si>
-    <t>Liliana Patricia Gómez Arias</t>
-  </si>
-  <si>
-    <t>164132-T</t>
-  </si>
-  <si>
-    <t>Proyectar Group S.A.S.</t>
-  </si>
-  <si>
-    <t>CL 63 A 46 14 OF 201</t>
-  </si>
-  <si>
-    <t>901829327-0</t>
-  </si>
-  <si>
-    <t>proyectargrpsas@gmail.com</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>NOMBRE DE LA ENTIDAD</t>
-  </si>
-  <si>
-    <t>DIRECCION DE LA ENTIDAD</t>
-  </si>
-  <si>
-    <t>número del Proceso de Contratación</t>
-  </si>
-  <si>
-    <t>Correo de la
-compañía 1:</t>
-  </si>
-  <si>
-    <t>NIT de la
-compañía 1:</t>
-  </si>
-  <si>
-    <t>Dirección de la
-compañía 1:</t>
-  </si>
-  <si>
-    <t>Nombre de la
-compañía 1:</t>
-  </si>
-  <si>
-    <t>Nombre de la contadora (en vez de revisor fiscal):</t>
-  </si>
-  <si>
-    <t>Cédula de la contador contadora (en vez de revisor fiscal):</t>
-  </si>
-  <si>
-    <t>Matrícula profesional de la contadora (en vez de revisor fiscal):</t>
-  </si>
-  <si>
-    <t>Objeto:</t>
-  </si>
-  <si>
-    <t>Teléfono de la
-compañía</t>
-  </si>
-  <si>
-    <t>MPRESA DE DESARROLLO URBANO RURAL INTEGRAL – EDURI E.I.C.E</t>
-  </si>
-  <si>
-    <t>Sonsón – Antioquia</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t xml:space="preserve">Atributo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre - representante legal:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Andrés Villa Llano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cédula - representante legal:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celular - representante legal:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrícula profesional - representante legal:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">011037-0508328 ANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de la contadora (en vez de revisor fiscal):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliana Patricia Gómez Arias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cédula de la contador contadora (en vez de revisor fiscal):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrícula profesional de la contadora (en vez de revisor fiscal):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164132-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyectar Group S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirección de la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL 63 A 46 14 OF 201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIT de la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">901829327-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correo de la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proyectargrpsas@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teléfono de la empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonsón – Antioquia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE DE LA ENTIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPRESA DE DESARROLLO URBANO RURAL INTEGRAL – EDURI E.I.C.E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECCION DE LA ENTIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objeto:</t>
   </si>
   <si>
     <t xml:space="preserve"> Mejoramiento de la cancha de fútbol del corregimiento de Jerusalén – Sonsón,Antioquia</t>
   </si>
   <si>
+    <t xml:space="preserve">número del Proceso de Contratación</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Invitación Privada EDURI 001-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisor Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indentificación revisor fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrícula profesional revisor fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">011037-0508328 MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cámara de comercio de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medellín</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,7 +157,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Consolas"/>
@@ -164,7 +187,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
@@ -172,17 +195,19 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -194,141 +219,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="2" tint="-0.1"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="7">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
+      <right style="medium"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
+      <right style="medium"/>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+  <cellXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -354,7 +419,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD1D1D1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -387,76 +452,60 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -488,7 +537,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -512,7 +561,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -572,26 +621,27 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultColWidth="10.57421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -607,23 +657,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="2" t="n">
         <v>1152446877</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="2" t="n">
         <v>3006974394</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -631,116 +681,158 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>43629386</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>3026141961</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B14" s="12" t="n">
+        <v>43831</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="2">
-        <v>43629386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B15" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="8">
-        <v>3026141961</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="10" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="10"/>
-    </row>
-    <row r="17" spans="1:2" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="B18" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="14" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
+      <c r="B19" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>123123333</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B12" r:id="rId1" display="proyectargrpsas@gmail.com"/>
   </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>